--- a/artfynd/A 33295-2022 artfynd.xlsx
+++ b/artfynd/A 33295-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33295-2022 artfynd.xlsx
+++ b/artfynd/A 33295-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3598,6 +3598,218 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122746803</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92143</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phellodon fuligineoalbus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Styggdalsbäcken SV, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>720201</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7171859</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122746802</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78044</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Svarttjärnen Ö, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>720100</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7171955</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33295-2022 artfynd.xlsx
+++ b/artfynd/A 33295-2022 artfynd.xlsx
@@ -3600,10 +3600,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122746803</v>
+        <v>122746802</v>
       </c>
       <c r="B27" t="n">
-        <v>92143</v>
+        <v>78146</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3616,34 +3616,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3100</v>
+        <v>6437</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken SV, Vb</t>
+          <t>Svarttjärnen Ö, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>720201</v>
+        <v>720100</v>
       </c>
       <c r="R27" t="n">
-        <v>7171859</v>
+        <v>7171955</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3706,10 +3706,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122746802</v>
+        <v>122746803</v>
       </c>
       <c r="B28" t="n">
-        <v>78044</v>
+        <v>92246</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3722,34 +3722,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>3100</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svarttjärnen Ö, Vb</t>
+          <t>Styggdalsbäcken SV, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720100</v>
+        <v>720201</v>
       </c>
       <c r="R28" t="n">
-        <v>7171955</v>
+        <v>7171859</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 33295-2022 artfynd.xlsx
+++ b/artfynd/A 33295-2022 artfynd.xlsx
@@ -3603,7 +3603,7 @@
         <v>122746802</v>
       </c>
       <c r="B27" t="n">
-        <v>78146</v>
+        <v>78150</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>122746803</v>
       </c>
       <c r="B28" t="n">
-        <v>92246</v>
+        <v>92250</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 33295-2022 artfynd.xlsx
+++ b/artfynd/A 33295-2022 artfynd.xlsx
@@ -3600,10 +3600,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122746802</v>
+        <v>122746803</v>
       </c>
       <c r="B27" t="n">
-        <v>78150</v>
+        <v>92250</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3616,34 +3616,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6437</v>
+        <v>3100</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svarttjärnen Ö, Vb</t>
+          <t>Styggdalsbäcken SV, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>720100</v>
+        <v>720201</v>
       </c>
       <c r="R27" t="n">
-        <v>7171955</v>
+        <v>7171859</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3706,10 +3706,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122746803</v>
+        <v>122746802</v>
       </c>
       <c r="B28" t="n">
-        <v>92250</v>
+        <v>78150</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3722,34 +3722,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3100</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken SV, Vb</t>
+          <t>Svarttjärnen Ö, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720201</v>
+        <v>720100</v>
       </c>
       <c r="R28" t="n">
-        <v>7171859</v>
+        <v>7171955</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 33295-2022 artfynd.xlsx
+++ b/artfynd/A 33295-2022 artfynd.xlsx
@@ -3600,10 +3600,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122746803</v>
+        <v>122746802</v>
       </c>
       <c r="B27" t="n">
-        <v>92250</v>
+        <v>78150</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3616,34 +3616,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3100</v>
+        <v>6437</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken SV, Vb</t>
+          <t>Svarttjärnen Ö, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>720201</v>
+        <v>720100</v>
       </c>
       <c r="R27" t="n">
-        <v>7171859</v>
+        <v>7171955</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3706,10 +3706,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122746802</v>
+        <v>122746803</v>
       </c>
       <c r="B28" t="n">
-        <v>78150</v>
+        <v>92250</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3722,34 +3722,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>3100</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svarttjärnen Ö, Vb</t>
+          <t>Styggdalsbäcken SV, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720100</v>
+        <v>720201</v>
       </c>
       <c r="R28" t="n">
-        <v>7171955</v>
+        <v>7171859</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 33295-2022 artfynd.xlsx
+++ b/artfynd/A 33295-2022 artfynd.xlsx
@@ -3600,10 +3600,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122746803</v>
+        <v>122746802</v>
       </c>
       <c r="B27" t="n">
-        <v>92250</v>
+        <v>78150</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3616,34 +3616,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3100</v>
+        <v>6437</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken SV, Vb</t>
+          <t>Svarttjärnen Ö, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>720201</v>
+        <v>720100</v>
       </c>
       <c r="R27" t="n">
-        <v>7171859</v>
+        <v>7171955</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3706,10 +3706,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122746802</v>
+        <v>122746803</v>
       </c>
       <c r="B28" t="n">
-        <v>78150</v>
+        <v>92258</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3722,34 +3722,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>3100</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svarttjärnen Ö, Vb</t>
+          <t>Styggdalsbäcken SV, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720100</v>
+        <v>720201</v>
       </c>
       <c r="R28" t="n">
-        <v>7171955</v>
+        <v>7171859</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 33295-2022 artfynd.xlsx
+++ b/artfynd/A 33295-2022 artfynd.xlsx
@@ -3603,7 +3603,7 @@
         <v>122746802</v>
       </c>
       <c r="B27" t="n">
-        <v>78150</v>
+        <v>78153</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>122746803</v>
       </c>
       <c r="B28" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 33295-2022 artfynd.xlsx
+++ b/artfynd/A 33295-2022 artfynd.xlsx
@@ -3603,7 +3603,7 @@
         <v>122746802</v>
       </c>
       <c r="B27" t="n">
-        <v>78153</v>
+        <v>78155</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>122746803</v>
       </c>
       <c r="B28" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 33295-2022 artfynd.xlsx
+++ b/artfynd/A 33295-2022 artfynd.xlsx
@@ -3603,7 +3603,7 @@
         <v>122746802</v>
       </c>
       <c r="B27" t="n">
-        <v>78718</v>
+        <v>78720</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>122746803</v>
       </c>
       <c r="B28" t="n">
-        <v>93202</v>
+        <v>93205</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 33295-2022 artfynd.xlsx
+++ b/artfynd/A 33295-2022 artfynd.xlsx
@@ -3603,7 +3603,7 @@
         <v>122746802</v>
       </c>
       <c r="B27" t="n">
-        <v>78720</v>
+        <v>78722</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>122746803</v>
       </c>
       <c r="B28" t="n">
-        <v>93205</v>
+        <v>93211</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 33295-2022 artfynd.xlsx
+++ b/artfynd/A 33295-2022 artfynd.xlsx
@@ -3603,7 +3603,7 @@
         <v>122746802</v>
       </c>
       <c r="B27" t="n">
-        <v>78722</v>
+        <v>78730</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>122746803</v>
       </c>
       <c r="B28" t="n">
-        <v>93211</v>
+        <v>93221</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 33295-2022 artfynd.xlsx
+++ b/artfynd/A 33295-2022 artfynd.xlsx
@@ -3704,7 +3704,7 @@
         <v>122746803</v>
       </c>
       <c r="B28" t="n">
-        <v>93221</v>
+        <v>93222</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 33295-2022 artfynd.xlsx
+++ b/artfynd/A 33295-2022 artfynd.xlsx
@@ -3603,7 +3603,7 @@
         <v>122746802</v>
       </c>
       <c r="B27" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>122746803</v>
       </c>
       <c r="B28" t="n">
-        <v>93222</v>
+        <v>93223</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 33295-2022 artfynd.xlsx
+++ b/artfynd/A 33295-2022 artfynd.xlsx
@@ -3704,7 +3704,7 @@
         <v>122746803</v>
       </c>
       <c r="B28" t="n">
-        <v>93223</v>
+        <v>93225</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 33295-2022 artfynd.xlsx
+++ b/artfynd/A 33295-2022 artfynd.xlsx
@@ -3603,7 +3603,7 @@
         <v>122746802</v>
       </c>
       <c r="B27" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>122746803</v>
       </c>
       <c r="B28" t="n">
-        <v>93225</v>
+        <v>93226</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 33295-2022 artfynd.xlsx
+++ b/artfynd/A 33295-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105315225</v>
+        <v>105315224</v>
       </c>
       <c r="B2" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4365</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720102.4575799959</v>
+        <v>720122</v>
       </c>
       <c r="R2" t="n">
-        <v>7171968.548380981</v>
+        <v>7171965</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105315214</v>
+        <v>105315097</v>
       </c>
       <c r="B3" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720282.2281984141</v>
+        <v>720025</v>
       </c>
       <c r="R3" t="n">
-        <v>7171809.737982399</v>
+        <v>7172025</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105315223</v>
+        <v>105315977</v>
       </c>
       <c r="B4" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4365</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720126.3044914468</v>
+        <v>720171</v>
       </c>
       <c r="R4" t="n">
-        <v>7171966.836234877</v>
+        <v>7171907</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,19 +947,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,37 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105315226</v>
+        <v>105315979</v>
       </c>
       <c r="B5" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4365</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720042.9814415342</v>
+        <v>720043</v>
       </c>
       <c r="R5" t="n">
-        <v>7172009.455877562</v>
+        <v>7172006</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,19 +1049,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105315216</v>
+        <v>105315214</v>
       </c>
       <c r="B6" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4365</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720171.247947294</v>
+        <v>720282</v>
       </c>
       <c r="R6" t="n">
-        <v>7171906.348375549</v>
+        <v>7171810</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,19 +1151,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105315217</v>
+        <v>105315215</v>
       </c>
       <c r="B7" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720165.6337075366</v>
+        <v>720190</v>
       </c>
       <c r="R7" t="n">
-        <v>7171936.095331642</v>
+        <v>7171899</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1333,19 +1253,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,37 +1287,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105315222</v>
+        <v>105315969</v>
       </c>
       <c r="B8" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4365</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720127.2560758173</v>
+        <v>720028</v>
       </c>
       <c r="R8" t="n">
-        <v>7171965.613088013</v>
+        <v>7172020</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1447,22 +1352,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,15 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105315969</v>
+        <v>105315978</v>
       </c>
       <c r="B9" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720027.5841521746</v>
+        <v>720133</v>
       </c>
       <c r="R9" t="n">
-        <v>7172019.536713675</v>
+        <v>7171957</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1564,22 +1454,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-09-06</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-09-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,15 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105315212</v>
+        <v>105315980</v>
       </c>
       <c r="B10" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1651,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720125.9260293526</v>
+        <v>719969</v>
       </c>
       <c r="R10" t="n">
-        <v>7171924.591712637</v>
+        <v>7171913</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1684,19 +1559,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,15 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105315977</v>
+        <v>122746803</v>
       </c>
       <c r="B11" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93296</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,37 +1604,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>3100</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Trehörningstjärnheden, Vb</t>
+          <t>Styggdalsbäcken SV, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720171.1856093023</v>
+        <v>720201</v>
       </c>
       <c r="R11" t="n">
-        <v>7171907.205425767</v>
+        <v>7171859</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1798,22 +1658,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,11 +1674,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>Elin Kollberg</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1841,41 +1686,40 @@
           <t>Elin Kollberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105315096</v>
+        <v>105315212</v>
       </c>
       <c r="B12" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1885,10 +1729,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720022.9340417578</v>
+        <v>720126</v>
       </c>
       <c r="R12" t="n">
-        <v>7172012.306317578</v>
+        <v>7171925</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1915,22 +1759,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-09-06</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-09-06</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,15 +1796,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105315220</v>
+        <v>105315218</v>
       </c>
       <c r="B13" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,10 +1831,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720128.2460578084</v>
+        <v>720156</v>
       </c>
       <c r="R13" t="n">
-        <v>7171957.930979285</v>
+        <v>7171927</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2035,19 +1864,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2079,37 +1898,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105315224</v>
+        <v>105315220</v>
       </c>
       <c r="B14" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>65</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2119,10 +1933,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720122.1386616197</v>
+        <v>720128</v>
       </c>
       <c r="R14" t="n">
-        <v>7171964.810157076</v>
+        <v>7171958</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2152,19 +1966,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2196,15 +2000,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105315215</v>
+        <v>105315094</v>
       </c>
       <c r="B15" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2212,21 +2011,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2236,10 +2035,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720190.3519789902</v>
+        <v>720084</v>
       </c>
       <c r="R15" t="n">
-        <v>7171898.691321844</v>
+        <v>7171853</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2266,22 +2065,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2313,37 +2102,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>105315213</v>
+        <v>105315219</v>
       </c>
       <c r="B16" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2353,10 +2137,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720148.1962895342</v>
+        <v>720144</v>
       </c>
       <c r="R16" t="n">
-        <v>7171908.979706295</v>
+        <v>7171928</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2386,19 +2170,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2430,15 +2204,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>105315978</v>
+        <v>105315221</v>
       </c>
       <c r="B17" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2446,21 +2215,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2470,10 +2239,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720133.4881380848</v>
+        <v>720126</v>
       </c>
       <c r="R17" t="n">
-        <v>7171957.019850194</v>
+        <v>7171969</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2503,19 +2272,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2547,37 +2306,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>105315980</v>
+        <v>105315095</v>
       </c>
       <c r="B18" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2079</v>
+        <v>4365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2587,10 +2341,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>719968.9232401268</v>
+        <v>720129</v>
       </c>
       <c r="R18" t="n">
-        <v>7171912.747606488</v>
+        <v>7171875</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2617,22 +2371,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2664,37 +2408,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>105315979</v>
+        <v>105315096</v>
       </c>
       <c r="B19" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2704,10 +2443,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720042.8327591962</v>
+        <v>720023</v>
       </c>
       <c r="R19" t="n">
-        <v>7172005.568092615</v>
+        <v>7172012</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2734,22 +2473,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2781,37 +2510,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>105315094</v>
+        <v>105315213</v>
       </c>
       <c r="B20" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2821,10 +2545,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720083.6839241034</v>
+        <v>720148</v>
       </c>
       <c r="R20" t="n">
-        <v>7171853.024040401</v>
+        <v>7171909</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2851,22 +2575,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-09-06</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-09-06</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2898,37 +2612,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>105315219</v>
+        <v>105315216</v>
       </c>
       <c r="B21" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2938,10 +2647,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720143.7904611053</v>
+        <v>720171</v>
       </c>
       <c r="R21" t="n">
-        <v>7171928.044830357</v>
+        <v>7171906</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2971,19 +2680,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3015,37 +2714,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>105315218</v>
+        <v>105315217</v>
       </c>
       <c r="B22" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3055,10 +2749,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720155.928621779</v>
+        <v>720166</v>
       </c>
       <c r="R22" t="n">
-        <v>7171927.204472467</v>
+        <v>7171936</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3088,19 +2782,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3132,37 +2816,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>105315221</v>
+        <v>105315222</v>
       </c>
       <c r="B23" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3172,10 +2851,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720126.1798403717</v>
+        <v>720127</v>
       </c>
       <c r="R23" t="n">
-        <v>7171968.550300481</v>
+        <v>7171966</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3205,19 +2884,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3249,15 +2918,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>105315095</v>
+        <v>105315223</v>
       </c>
       <c r="B24" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3289,10 +2953,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720128.6827948461</v>
+        <v>720126</v>
       </c>
       <c r="R24" t="n">
-        <v>7171874.820292912</v>
+        <v>7171967</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3319,22 +2983,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-09-06</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-09-06</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3366,37 +3020,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>105953761</v>
+        <v>105315225</v>
       </c>
       <c r="B25" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>4365</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3406,10 +3055,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720093.5793790503</v>
+        <v>720102</v>
       </c>
       <c r="R25" t="n">
-        <v>7171960.148735683</v>
+        <v>7171969</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3439,19 +3088,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3476,22 +3115,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Via Helene Andersson</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>106232485</v>
+        <v>105315226</v>
       </c>
       <c r="B26" t="n">
-        <v>88019</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3499,42 +3133,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6276</v>
+        <v>4365</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Trehörningstjärnheden, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>719654.9985721407</v>
+        <v>720043</v>
       </c>
       <c r="R26" t="n">
-        <v>7171691.784949192</v>
+        <v>7172009</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3558,22 +3187,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3584,11 +3203,16 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -3600,48 +3224,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122746802</v>
+        <v>106232485</v>
       </c>
       <c r="B27" t="n">
-        <v>78735</v>
+        <v>90691</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6437</v>
+        <v>6276</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svarttjärnen Ö, Vb</t>
+          <t>Trehörningstjärnheden, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>720100</v>
+        <v>719655</v>
       </c>
       <c r="R27" t="n">
-        <v>7171955</v>
+        <v>7171692</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3665,12 +3294,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2022-08-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2022-08-19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3685,7 +3314,7 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -3693,18 +3322,14 @@
           <t>Elin Kollberg</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122746803</v>
+        <v>122746802</v>
       </c>
       <c r="B28" t="n">
-        <v>93230</v>
+        <v>78776</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,34 +3337,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3100</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken SV, Vb</t>
+          <t>Svarttjärnen Ö, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720201</v>
+        <v>720100</v>
       </c>
       <c r="R28" t="n">
-        <v>7171859</v>
+        <v>7171955</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3799,6 +3424,108 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>105953761</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Trehörningstjärnheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>720094</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7171960</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Via Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33295-2022 artfynd.xlsx
+++ b/artfynd/A 33295-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315224</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315097</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315977</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315979</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315214</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315215</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315969</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315978</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315980</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1691,6 +1741,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122746803</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1793,6 +1848,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315212</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1895,6 +1955,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315218</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1997,6 +2062,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315220</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2099,6 +2169,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315094</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2201,6 +2276,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315219</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2303,6 +2383,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315221</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2405,6 +2490,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315095</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2507,6 +2597,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315096</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2609,6 +2704,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315213</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2711,6 +2811,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315216</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2813,6 +2918,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315217</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2915,6 +3025,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315222</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3017,6 +3132,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315223</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3119,6 +3239,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315225</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3221,6 +3346,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315226</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3323,6 +3453,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106232485</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3424,6 +3559,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122746802</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3526,8 +3666,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105953761</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>